--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,207 +49,192 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.08.2026</x:t>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISVEA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARCL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAYLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
     <x:t>11.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISVEA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARCL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAYLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
     <x:t>DGNMO</x:t>
   </x:si>
   <x:si>
@@ -259,6 +244,18 @@
     <x:t>KARSN</x:t>
   </x:si>
   <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -283,6 +280,12 @@
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
+    <x:t>20.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.08.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>PYAYN</x:t>
   </x:si>
   <x:si>
@@ -299,12 +302,6 @@
   </x:si>
   <x:si>
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.08.2026</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -655,7 +652,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K127"/>
+  <x:dimension ref="A1:K120"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -742,10 +739,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>15</x:v>
@@ -765,20 +762,20 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -789,18 +786,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -809,10 +806,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>14</x:v>
@@ -835,7 +832,7 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -844,13 +841,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>15</x:v>
@@ -879,13 +876,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>15</x:v>
@@ -905,19 +902,19 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -949,10 +946,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -975,19 +972,19 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -1010,19 +1007,19 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>14</x:v>
@@ -1054,10 +1051,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
@@ -1095,7 +1092,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>15</x:v>
@@ -1200,7 +1197,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>15</x:v>
@@ -1232,7 +1229,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
@@ -1255,7 +1252,7 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1267,7 +1264,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
@@ -1290,7 +1287,7 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1299,13 +1296,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>15</x:v>
@@ -1314,30 +1311,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>14</x:v>
@@ -1369,10 +1366,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>14</x:v>
@@ -1404,13 +1401,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>15</x:v>
@@ -1419,18 +1416,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1439,10 +1436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>14</x:v>
@@ -1465,7 +1462,7 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0">
         <x:v>0</x:v>
@@ -1474,10 +1471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
@@ -1500,7 +1497,7 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1509,10 +1506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
@@ -1535,7 +1532,7 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1544,10 +1541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>14</x:v>
@@ -1570,7 +1567,7 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1579,10 +1576,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>14</x:v>
@@ -1605,7 +1602,7 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="0">
         <x:v>0</x:v>
@@ -1617,7 +1614,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>14</x:v>
@@ -1640,19 +1637,19 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>14</x:v>
@@ -1675,7 +1672,7 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1684,10 +1681,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>14</x:v>
@@ -1710,7 +1707,7 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1719,7 +1716,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
         <x:v>70</x:v>
@@ -1745,7 +1742,7 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B32" s="0">
         <x:v>0</x:v>
@@ -1757,7 +1754,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>14</x:v>
@@ -1789,13 +1786,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
         <x:v>15</x:v>
@@ -1804,18 +1801,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B34" s="0">
         <x:v>0</x:v>
@@ -1824,10 +1821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>14</x:v>
@@ -1850,19 +1847,19 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>14</x:v>
@@ -1894,13 +1891,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>15</x:v>
@@ -1909,70 +1906,52 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:11">
-      <x:c r="A37" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:11">
+      <x:c r="A38" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G37" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H37" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I37" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J37" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K37" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>81</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
@@ -1980,10 +1959,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>12</x:v>
@@ -1994,19 +1973,19 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
@@ -2014,16 +1993,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -2031,438 +2010,438 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>38</x:v>
@@ -2470,16 +2449,16 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>38</x:v>
@@ -2487,257 +2466,257 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E84" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E85" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
@@ -2745,33 +2724,33 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
@@ -2779,135 +2758,135 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
@@ -2915,33 +2894,33 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
@@ -2949,33 +2928,33 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -2983,183 +2962,183 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
         <x:v>70</x:v>
@@ -3167,16 +3146,16 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
         <x:v>70</x:v>
@@ -3184,36 +3163,36 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
@@ -3221,101 +3200,101 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E118" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D119" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E119" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
@@ -3323,135 +3302,16 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:11">
-      <x:c r="A121" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D121" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E121" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:11">
-      <x:c r="A122" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C122" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D122" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E122" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:11">
-      <x:c r="A123" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D123" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E123" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:11">
-      <x:c r="A124" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D124" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E124" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:11">
-      <x:c r="A125" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E125" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:11">
-      <x:c r="A126" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D126" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E126" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:11">
-      <x:c r="A127" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D127" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E127" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -254,6 +254,21 @@
   </x:si>
   <x:si>
     <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -652,7 +667,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K120"/>
+  <x:dimension ref="A1:K129"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1915,125 +1930,179 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="37" spans="1:11">
+      <x:c r="A37" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C39" s="0" t="s">
+      <x:c r="E39" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:11">
-      <x:c r="A40" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>18</x:v>
@@ -2041,16 +2110,16 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>18</x:v>
@@ -2058,16 +2127,16 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>18</x:v>
@@ -2075,16 +2144,16 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>18</x:v>
@@ -2092,16 +2161,16 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>18</x:v>
@@ -2109,16 +2178,16 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>18</x:v>
@@ -2126,16 +2195,16 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>18</x:v>
@@ -2143,16 +2212,16 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>18</x:v>
@@ -2160,13 +2229,13 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>24</x:v>
@@ -2177,64 +2246,64 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>27</x:v>
@@ -2245,67 +2314,67 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>32</x:v>
@@ -2313,16 +2382,16 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
         <x:v>32</x:v>
@@ -2330,13 +2399,13 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>34</x:v>
@@ -2347,67 +2416,67 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>38</x:v>
@@ -2415,16 +2484,16 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
         <x:v>38</x:v>
@@ -2432,13 +2501,13 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>40</x:v>
@@ -2449,13 +2518,13 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>40</x:v>
@@ -2466,98 +2535,98 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>46</x:v>
@@ -2568,53 +2637,53 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
@@ -2628,7 +2697,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>51</x:v>
@@ -2639,13 +2708,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>51</x:v>
@@ -2656,13 +2725,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>51</x:v>
@@ -2670,13 +2739,13 @@
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>53</x:v>
@@ -2687,13 +2756,13 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>53</x:v>
@@ -2704,13 +2773,13 @@
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>53</x:v>
@@ -2721,13 +2790,13 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>53</x:v>
@@ -2738,13 +2807,13 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>53</x:v>
@@ -2755,13 +2824,13 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>53</x:v>
@@ -2772,16 +2841,16 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
         <x:v>51</x:v>
@@ -2789,16 +2858,16 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>51</x:v>
@@ -2806,16 +2875,16 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
         <x:v>51</x:v>
@@ -2823,13 +2892,13 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>57</x:v>
@@ -2840,13 +2909,13 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>57</x:v>
@@ -2857,13 +2926,13 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>57</x:v>
@@ -2874,13 +2943,13 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>57</x:v>
@@ -2891,13 +2960,13 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>57</x:v>
@@ -2908,13 +2977,13 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>57</x:v>
@@ -2925,13 +2994,13 @@
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>57</x:v>
@@ -2942,135 +3011,135 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
         <x:v>70</x:v>
@@ -3078,16 +3147,16 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
         <x:v>70</x:v>
@@ -3095,13 +3164,13 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>72</x:v>
@@ -3112,13 +3181,13 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>72</x:v>
@@ -3129,13 +3198,13 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>72</x:v>
@@ -3146,13 +3215,13 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>72</x:v>
@@ -3166,10 +3235,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>72</x:v>
@@ -3183,10 +3252,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>72</x:v>
@@ -3200,10 +3269,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>72</x:v>
@@ -3214,13 +3283,13 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>72</x:v>
@@ -3231,13 +3300,13 @@
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>72</x:v>
@@ -3248,70 +3317,223 @@
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
         <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:11">
+      <x:c r="A121" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:11">
+      <x:c r="A122" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E122" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:11">
+      <x:c r="A123" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:11">
+      <x:c r="A124" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:11">
+      <x:c r="A125" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E125" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:11">
+      <x:c r="A126" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E126" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:11">
+      <x:c r="A127" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:11">
+      <x:c r="A128" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:11">
+      <x:c r="A129" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E129" s="0" t="s">
+        <x:v>82</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -271,6 +271,15 @@
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -307,16 +316,16 @@
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEIAK</x:t>
   </x:si>
   <x:si>
     <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -667,7 +676,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K129"/>
+  <x:dimension ref="A1:K135"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -2035,94 +2044,130 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="40" spans="1:11">
+      <x:c r="A40" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:11">
-      <x:c r="A42" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>4</x:v>
+      <x:c r="F41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
@@ -2130,13 +2175,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>18</x:v>
@@ -2144,16 +2189,16 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>18</x:v>
@@ -2161,16 +2206,16 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>18</x:v>
@@ -2181,13 +2226,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>18</x:v>
@@ -2195,16 +2240,16 @@
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>18</x:v>
@@ -2212,16 +2257,16 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>18</x:v>
@@ -2229,16 +2274,16 @@
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>18</x:v>
@@ -2246,16 +2291,16 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
         <x:v>18</x:v>
@@ -2263,13 +2308,13 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>24</x:v>
@@ -2280,13 +2325,13 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>24</x:v>
@@ -2297,47 +2342,47 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>27</x:v>
@@ -2348,13 +2393,13 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>27</x:v>
@@ -2365,50 +2410,50 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>32</x:v>
@@ -2416,16 +2461,16 @@
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>32</x:v>
@@ -2433,13 +2478,13 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>34</x:v>
@@ -2450,13 +2495,13 @@
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>34</x:v>
@@ -2467,36 +2512,36 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -2504,13 +2549,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>38</x:v>
@@ -2518,16 +2563,16 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>38</x:v>
@@ -2535,13 +2580,13 @@
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>40</x:v>
@@ -2552,13 +2597,13 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>40</x:v>
@@ -2569,13 +2614,13 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>40</x:v>
@@ -2586,81 +2631,81 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>46</x:v>
@@ -2671,13 +2716,13 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>46</x:v>
@@ -2688,36 +2733,36 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
@@ -2725,13 +2770,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>51</x:v>
@@ -2742,13 +2787,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
         <x:v>51</x:v>
@@ -2759,13 +2804,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>51</x:v>
@@ -2776,10 +2821,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>53</x:v>
@@ -2790,13 +2835,13 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>53</x:v>
@@ -2807,13 +2852,13 @@
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>53</x:v>
@@ -2824,13 +2869,13 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>53</x:v>
@@ -2841,13 +2886,13 @@
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>53</x:v>
@@ -2858,13 +2903,13 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>53</x:v>
@@ -2875,13 +2920,13 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>53</x:v>
@@ -2892,16 +2937,16 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
         <x:v>51</x:v>
@@ -2909,16 +2954,16 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
         <x:v>51</x:v>
@@ -2926,13 +2971,13 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>57</x:v>
@@ -2943,13 +2988,13 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>57</x:v>
@@ -2960,13 +3005,13 @@
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>57</x:v>
@@ -2977,13 +3022,13 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>57</x:v>
@@ -2994,13 +3039,13 @@
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>57</x:v>
@@ -3011,13 +3056,13 @@
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>57</x:v>
@@ -3028,13 +3073,13 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>57</x:v>
@@ -3045,13 +3090,13 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>57</x:v>
@@ -3062,118 +3107,118 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
         <x:v>70</x:v>
@@ -3181,16 +3226,16 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
         <x:v>70</x:v>
@@ -3198,13 +3243,13 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>72</x:v>
@@ -3215,13 +3260,13 @@
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>72</x:v>
@@ -3232,13 +3277,13 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>72</x:v>
@@ -3249,13 +3294,13 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>72</x:v>
@@ -3269,10 +3314,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>72</x:v>
@@ -3286,10 +3331,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>72</x:v>
@@ -3303,10 +3348,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>72</x:v>
@@ -3320,10 +3365,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>72</x:v>
@@ -3334,13 +3379,13 @@
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>72</x:v>
@@ -3351,13 +3396,13 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>72</x:v>
@@ -3368,47 +3413,47 @@
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>77</x:v>
@@ -3419,13 +3464,13 @@
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>77</x:v>
@@ -3436,47 +3481,47 @@
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>81</x:v>
@@ -3487,13 +3532,13 @@
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>81</x:v>
@@ -3504,13 +3549,13 @@
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>81</x:v>
@@ -3521,19 +3566,121 @@
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
         <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:11">
+      <x:c r="A130" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:11">
+      <x:c r="A131" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E131" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:11">
+      <x:c r="A132" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E132" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:11">
+      <x:c r="A133" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:11">
+      <x:c r="A134" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:11">
+      <x:c r="A135" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
+        <x:v>86</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,231 +49,225 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.08.2026</x:t>
+    <x:t>ISVEA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARCL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAYLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
   </x:si>
   <x:si>
     <x:t>16.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISVEA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARCL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAYLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKSLN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>15.10.2026</x:t>
   </x:si>
   <x:si>
@@ -289,18 +283,18 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
     <x:t>Açığa Satış Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
@@ -316,16 +310,16 @@
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PPEGK</x:t>
   </x:si>
   <x:si>
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -676,7 +670,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K135"/>
+  <x:dimension ref="A1:K132"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -734,19 +728,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -763,100 +757,100 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -865,33 +859,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -903,25 +897,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -935,63 +929,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1008,30 +1002,30 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -1040,33 +1034,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -1078,25 +1072,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1113,30 +1107,30 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1145,33 +1139,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1183,25 +1177,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1221,22 +1215,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1250,54 +1244,54 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>14</x:v>
@@ -1323,16 +1317,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>15</x:v>
@@ -1346,7 +1340,7 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1355,33 +1349,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1390,33 +1384,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1425,33 +1419,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1460,33 +1454,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="0">
         <x:v>0</x:v>
@@ -1495,33 +1489,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1530,33 +1524,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1565,63 +1559,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1641,22 +1635,22 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1676,22 +1670,22 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -1708,30 +1702,30 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1740,33 +1734,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B32" s="0">
         <x:v>0</x:v>
@@ -1775,19 +1769,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
         <x:v>14</x:v>
@@ -1801,7 +1795,7 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1810,19 +1804,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
         <x:v>15</x:v>
@@ -1836,37 +1830,37 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
@@ -1880,63 +1874,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
@@ -1950,33 +1944,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B38" s="0">
         <x:v>0</x:v>
@@ -1985,63 +1979,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -2055,73 +2049,55 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:11">
+      <x:c r="A42" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:11">
-      <x:c r="A41" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K41" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
         <x:v>88</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>89</x:v>
@@ -2130,10 +2106,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -2161,10 +2137,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>13</x:v>
@@ -2184,7 +2160,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2192,16 +2168,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -2209,118 +2185,118 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -2328,38 +2304,38 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>91</x:v>
@@ -2371,7 +2347,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
@@ -2379,67 +2355,67 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D62" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -2456,41 +2432,41 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
@@ -2498,21 +2474,21 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>91</x:v>
@@ -2524,24 +2500,24 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -2549,16 +2525,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
@@ -2566,50 +2542,50 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
@@ -2617,38 +2593,38 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>91</x:v>
@@ -2657,10 +2633,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
@@ -2668,10 +2644,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>43</x:v>
@@ -2682,13 +2658,13 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>43</x:v>
@@ -2702,21 +2678,21 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>91</x:v>
@@ -2725,95 +2701,95 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -2821,16 +2797,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
@@ -2838,50 +2814,50 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -2889,55 +2865,55 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>91</x:v>
@@ -2946,10 +2922,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
@@ -2957,21 +2933,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>91</x:v>
@@ -2980,10 +2956,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
@@ -2991,38 +2967,38 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>91</x:v>
@@ -3031,49 +3007,49 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>91</x:v>
@@ -3082,49 +3058,49 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E102" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>91</x:v>
@@ -3133,10 +3109,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -3144,10 +3120,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>63</x:v>
@@ -3158,19 +3134,19 @@
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
@@ -3192,16 +3168,16 @@
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
         <x:v>67</x:v>
@@ -3212,50 +3188,50 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -3263,186 +3239,186 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D119" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E120" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D121" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E121" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
@@ -3450,67 +3426,67 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D124" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E124" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E125" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E125" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
@@ -3518,38 +3494,38 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>91</x:v>
@@ -3558,61 +3534,61 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D129" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E130" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D130" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E130" s="0" t="s">
-        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E131" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C131" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D131" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E131" s="0" t="s">
-        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
@@ -3626,61 +3602,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:11">
-      <x:c r="A133" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C133" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D133" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E133" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:11">
-      <x:c r="A134" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E134" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" spans="1:11">
-      <x:c r="A135" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D135" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E135" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -2270,10 +2270,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>21</x:v>
@@ -2287,10 +2287,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>21</x:v>
@@ -2304,10 +2304,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>24</x:v>
@@ -2321,10 +2321,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>24</x:v>
@@ -2474,10 +2474,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>34</x:v>
@@ -2491,10 +2491,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>34</x:v>
@@ -2593,10 +2593,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>40</x:v>
@@ -2610,10 +2610,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>40</x:v>
@@ -2865,10 +2865,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>50</x:v>
@@ -2882,10 +2882,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>50</x:v>
@@ -3069,10 +3069,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>60</x:v>
@@ -3086,10 +3086,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>60</x:v>
@@ -3171,10 +3171,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>69</x:v>
@@ -3188,10 +3188,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>69</x:v>
@@ -3205,10 +3205,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>69</x:v>
@@ -3222,10 +3222,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>69</x:v>
@@ -3239,10 +3239,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>69</x:v>
@@ -3256,10 +3256,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>69</x:v>
@@ -3290,10 +3290,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>69</x:v>
@@ -3307,10 +3307,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>69</x:v>
@@ -3324,10 +3324,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>69</x:v>
@@ -3341,10 +3341,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>69</x:v>
@@ -3358,10 +3358,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>69</x:v>
@@ -3375,10 +3375,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>74</x:v>
@@ -3392,10 +3392,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>74</x:v>
@@ -3409,10 +3409,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>74</x:v>
@@ -3426,10 +3426,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>74</x:v>
@@ -3443,10 +3443,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>78</x:v>
@@ -3460,10 +3460,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>78</x:v>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,51 +49,21 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>ISVEA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.09.2026</x:t>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
   </x:si>
   <x:si>
     <x:t>Evet</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARCL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.09.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>YAYLA</x:t>
   </x:si>
   <x:si>
@@ -283,43 +253,40 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKISY</x:t>
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
-    <x:t>20.08.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>03.08.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PYAYN</x:t>
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -670,7 +637,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K132"/>
+  <x:dimension ref="A1:K115"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -728,19 +695,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -754,7 +721,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
@@ -763,54 +730,54 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -827,25 +794,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -862,25 +829,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -903,19 +870,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -929,98 +896,98 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
+      <x:c r="E10" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -1034,63 +1001,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="E12" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1107,16 +1074,16 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>15</x:v>
@@ -1130,42 +1097,42 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1177,25 +1144,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1209,33 +1176,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1244,33 +1211,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1279,19 +1246,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>14</x:v>
@@ -1305,7 +1272,7 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1314,33 +1281,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1349,33 +1316,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1384,33 +1351,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1419,33 +1386,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1454,103 +1421,103 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1559,54 +1526,54 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
         <x:v>15</x:v>
@@ -1629,68 +1596,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1699,33 +1666,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="0">
         <x:v>0</x:v>
@@ -1734,33 +1701,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B32" s="0">
         <x:v>0</x:v>
@@ -1769,19 +1736,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
         <x:v>14</x:v>
@@ -1795,7 +1762,7 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1804,68 +1771,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>-1.9262</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
+      <x:c r="E34" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B35" s="0">
         <x:v>0</x:v>
@@ -1874,621 +1841,531 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:11">
-      <x:c r="A36" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G36" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H36" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I36" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J36" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G37" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H37" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I37" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J37" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B38" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G38" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H38" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I38" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J38" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G39" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I39" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J39" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:11">
+      <x:c r="A41" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>89</x:v>
@@ -2497,163 +2374,163 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E71" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E72" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
@@ -2661,33 +2538,33 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
@@ -2695,101 +2572,101 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -2797,191 +2674,191 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>89</x:v>
@@ -2990,214 +2867,214 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E97" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E98" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D107" s="0" t="s">
+      <x:c r="E107" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E107" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
+      <x:c r="E108" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E108" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -3205,33 +3082,33 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E109" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E110" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -3239,373 +3116,84 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E111" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E111" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:11">
-      <x:c r="A116" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E116" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:11">
-      <x:c r="A117" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E117" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:11">
-      <x:c r="A118" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E118" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:11">
-      <x:c r="A119" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D119" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="E119" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:11">
-      <x:c r="A120" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E120" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:11">
-      <x:c r="A121" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D121" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E121" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:11">
-      <x:c r="A122" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C122" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D122" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E122" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:11">
-      <x:c r="A123" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D123" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E123" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:11">
-      <x:c r="A124" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D124" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E124" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:11">
-      <x:c r="A125" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E125" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:11">
-      <x:c r="A126" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D126" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E126" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:11">
-      <x:c r="A127" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D127" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E127" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:11">
-      <x:c r="A128" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D128" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E128" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:11">
-      <x:c r="A129" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D129" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E129" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:11">
-      <x:c r="A130" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D130" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E130" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" spans="1:11">
-      <x:c r="A131" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C131" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D131" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E131" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" spans="1:11">
-      <x:c r="A132" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C132" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D132" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E132" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -1730,10 +1730,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>0</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0</x:v>
+        <x:v>-9.96</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>68</x:v>
@@ -1803,7 +1803,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>-1.9262</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>73</x:v>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -244,6 +244,15 @@
     <x:t>KZGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.10.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -271,16 +280,16 @@
     <x:t>03.08.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEIAK</x:t>
   </x:si>
   <x:si>
     <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>PYAYN</x:t>
@@ -637,7 +646,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K115"/>
+  <x:dimension ref="A1:K118"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1730,10 +1739,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>-9.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>68</x:v>
@@ -1865,43 +1874,61 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:11">
-      <x:c r="A37" s="0" t="s">
+    <x:row r="36" spans="1:11">
+      <x:c r="A36" s="0" t="s">
         <x:v>76</x:v>
+      </x:c>
+      <x:c r="B36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>-9.9343</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J36" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -1909,10 +1936,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>12</x:v>
@@ -1923,13 +1950,13 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>12</x:v>
@@ -1943,10 +1970,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>12</x:v>
@@ -1957,19 +1984,19 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -1977,10 +2004,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>18</x:v>
@@ -1991,16 +2018,16 @@
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>19</x:v>
@@ -2011,10 +2038,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>21</x:v>
@@ -2025,13 +2052,13 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>21</x:v>
@@ -2045,10 +2072,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>21</x:v>
@@ -2059,19 +2086,19 @@
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -2079,10 +2106,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>24</x:v>
@@ -2096,13 +2123,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>25</x:v>
@@ -2110,13 +2137,13 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>27</x:v>
@@ -2130,10 +2157,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>27</x:v>
@@ -2144,13 +2171,13 @@
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>27</x:v>
@@ -2164,10 +2191,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>27</x:v>
@@ -2178,19 +2205,19 @@
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
@@ -2198,10 +2225,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>30</x:v>
@@ -2212,19 +2239,19 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
@@ -2232,10 +2259,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>33</x:v>
@@ -2246,13 +2273,13 @@
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>33</x:v>
@@ -2266,10 +2293,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>33</x:v>
@@ -2280,19 +2307,19 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -2300,10 +2327,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>37</x:v>
@@ -2317,13 +2344,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>38</x:v>
@@ -2334,13 +2361,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>38</x:v>
@@ -2351,10 +2378,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>40</x:v>
@@ -2368,10 +2395,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>40</x:v>
@@ -2382,13 +2409,13 @@
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>40</x:v>
@@ -2402,10 +2429,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>40</x:v>
@@ -2416,13 +2443,13 @@
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>40</x:v>
@@ -2436,10 +2463,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>40</x:v>
@@ -2450,13 +2477,13 @@
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>40</x:v>
@@ -2470,10 +2497,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>40</x:v>
@@ -2484,16 +2511,16 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
         <x:v>38</x:v>
@@ -2504,10 +2531,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>44</x:v>
@@ -2518,13 +2545,13 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>44</x:v>
@@ -2538,10 +2565,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>44</x:v>
@@ -2552,13 +2579,13 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>44</x:v>
@@ -2572,10 +2599,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>44</x:v>
@@ -2586,13 +2613,13 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>44</x:v>
@@ -2606,10 +2633,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>44</x:v>
@@ -2620,13 +2647,13 @@
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>44</x:v>
@@ -2640,10 +2667,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>44</x:v>
@@ -2654,19 +2681,19 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -2674,10 +2701,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>50</x:v>
@@ -2688,19 +2715,19 @@
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
@@ -2708,10 +2735,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>53</x:v>
@@ -2722,19 +2749,19 @@
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -2742,10 +2769,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>56</x:v>
@@ -2756,16 +2783,16 @@
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>57</x:v>
@@ -2776,10 +2803,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>59</x:v>
@@ -2790,13 +2817,13 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>59</x:v>
@@ -2810,10 +2837,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>59</x:v>
@@ -2824,13 +2851,13 @@
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>59</x:v>
@@ -2844,10 +2871,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>59</x:v>
@@ -2861,10 +2888,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>59</x:v>
@@ -2878,10 +2905,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>59</x:v>
@@ -2895,10 +2922,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>59</x:v>
@@ -2912,10 +2939,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>59</x:v>
@@ -2926,13 +2953,13 @@
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>59</x:v>
@@ -2946,10 +2973,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>59</x:v>
@@ -2960,19 +2987,19 @@
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
@@ -2980,10 +3007,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>64</x:v>
@@ -2994,13 +3021,13 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>64</x:v>
@@ -3014,10 +3041,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>64</x:v>
@@ -3028,19 +3055,19 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -3048,10 +3075,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>68</x:v>
@@ -3062,13 +3089,13 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>68</x:v>
@@ -3082,10 +3109,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>68</x:v>
@@ -3096,13 +3123,13 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>68</x:v>
@@ -3116,10 +3143,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>68</x:v>
@@ -3130,19 +3157,19 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
@@ -3150,10 +3177,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>73</x:v>
@@ -3164,13 +3191,13 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>73</x:v>
@@ -3184,16 +3211,67 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
         <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:11">
+      <x:c r="A116" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:11">
+      <x:c r="A117" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:11">
+      <x:c r="A118" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
+        <x:v>78</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -262,40 +262,40 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
     <x:t>Açığa Satış Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
     <x:t>03.08.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PPEGK</x:t>
   </x:si>
   <x:si>
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -899,10 +899,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>27</x:v>
@@ -1109,10 +1109,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>0</x:v>
+        <x:v>71.7</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>0</x:v>
+        <x:v>9.97</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>40</x:v>
@@ -1882,7 +1882,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>-9.9343</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>77</x:v>
@@ -1970,10 +1970,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>12</x:v>
@@ -1987,10 +1987,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>12</x:v>
@@ -2004,10 +2004,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>18</x:v>
@@ -2021,10 +2021,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>18</x:v>
@@ -2072,10 +2072,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>21</x:v>
@@ -2089,10 +2089,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>21</x:v>
@@ -2157,10 +2157,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>27</x:v>
@@ -2174,10 +2174,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>27</x:v>
@@ -2259,10 +2259,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>33</x:v>
@@ -2276,10 +2276,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>33</x:v>
@@ -2293,10 +2293,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>33</x:v>
@@ -2310,10 +2310,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>33</x:v>
@@ -2429,10 +2429,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>40</x:v>
@@ -2446,10 +2446,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>40</x:v>
@@ -2531,10 +2531,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>44</x:v>
@@ -2548,10 +2548,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>44</x:v>
@@ -2565,10 +2565,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>44</x:v>
@@ -2582,10 +2582,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>44</x:v>
@@ -2599,10 +2599,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>44</x:v>
@@ -2616,10 +2616,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>44</x:v>
@@ -2701,10 +2701,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>50</x:v>
@@ -2718,10 +2718,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>50</x:v>
@@ -2735,10 +2735,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>53</x:v>
@@ -2752,10 +2752,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>53</x:v>
@@ -2769,10 +2769,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>56</x:v>
@@ -2786,10 +2786,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>56</x:v>
@@ -2837,10 +2837,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>59</x:v>
@@ -2854,10 +2854,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>59</x:v>
@@ -2871,10 +2871,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>59</x:v>
@@ -2888,10 +2888,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>59</x:v>
@@ -2905,10 +2905,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>59</x:v>
@@ -2939,10 +2939,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>59</x:v>
@@ -2956,10 +2956,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>59</x:v>
@@ -2973,10 +2973,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>59</x:v>
@@ -2990,10 +2990,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>59</x:v>
@@ -3007,10 +3007,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>64</x:v>
@@ -3024,10 +3024,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>64</x:v>
@@ -3245,10 +3245,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>77</x:v>
@@ -3262,10 +3262,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>77</x:v>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,13 +49,13 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.09.2026</x:t>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.09.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
@@ -64,18 +64,6 @@
     <x:t>Evet</x:t>
   </x:si>
   <x:si>
-    <x:t>YAYLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.09.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>GIPTA</x:t>
   </x:si>
   <x:si>
@@ -253,6 +241,12 @@
     <x:t>22.10.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.10.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -262,40 +256,40 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKISY</x:t>
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
     <x:t>03.08.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PYAYN</x:t>
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -646,7 +640,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K118"/>
+  <x:dimension ref="A1:K115"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -730,7 +724,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
@@ -756,19 +750,19 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
@@ -791,22 +785,22 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="E5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>15</x:v>
@@ -835,10 +829,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
@@ -861,22 +855,22 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>15</x:v>
@@ -896,19 +890,19 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -940,10 +934,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -966,19 +960,19 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
+      <x:c r="E10" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -1016,7 +1010,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>15</x:v>
@@ -1025,13 +1019,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -1045,7 +1039,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>34</x:v>
@@ -1071,22 +1065,22 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>273.5</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>-9.96</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>15</x:v>
@@ -1095,30 +1089,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>71.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>9.97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>14</x:v>
@@ -1141,7 +1135,7 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1153,7 +1147,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>14</x:v>
@@ -1176,7 +1170,7 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1188,7 +1182,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>14</x:v>
@@ -1211,7 +1205,7 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1220,10 +1214,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
@@ -1246,19 +1240,19 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>0</x:v>
+        <x:v>9.34</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>0</x:v>
+        <x:v>-9.93</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>14</x:v>
@@ -1281,7 +1275,7 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1290,10 +1284,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>14</x:v>
@@ -1316,19 +1310,19 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>14</x:v>
@@ -1360,10 +1354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>14</x:v>
@@ -1386,7 +1380,7 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1395,10 +1389,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>14</x:v>
@@ -1421,7 +1415,7 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1430,10 +1424,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>14</x:v>
@@ -1456,19 +1450,19 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
@@ -1491,7 +1485,7 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1500,13 +1494,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
         <x:v>15</x:v>
@@ -1515,18 +1509,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B26" s="0">
         <x:v>0</x:v>
@@ -1535,10 +1529,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>14</x:v>
@@ -1561,22 +1555,22 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
         <x:v>15</x:v>
@@ -1585,13 +1579,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1599,16 +1593,16 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>14</x:v>
@@ -1710,10 +1704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>14</x:v>
@@ -1736,19 +1730,19 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>14</x:v>
@@ -1780,10 +1774,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>14</x:v>
@@ -1850,10 +1844,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>14</x:v>
@@ -1874,49 +1868,31 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:11">
-      <x:c r="A36" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
+    <x:row r="37" spans="1:11">
+      <x:c r="A37" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G36" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H36" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I36" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J36" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K36" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
         <x:v>79</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>80</x:v>
@@ -1925,10 +1901,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -1950,16 +1926,16 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
         <x:v>13</x:v>
@@ -1970,13 +1946,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
         <x:v>13</x:v>
@@ -1984,7 +1960,7 @@
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>82</x:v>
@@ -1993,7 +1969,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
         <x:v>13</x:v>
@@ -2001,24 +1977,24 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>82</x:v>
@@ -2027,44 +2003,44 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
+      <x:c r="E46" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2072,16 +2048,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -2089,101 +2065,101 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
+      <x:c r="E53" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
@@ -2191,21 +2167,21 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>82</x:v>
@@ -2214,44 +2190,44 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
+      <x:c r="E57" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
@@ -2259,10 +2235,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>33</x:v>
@@ -2276,13 +2252,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
         <x:v>34</x:v>
@@ -2290,16 +2266,16 @@
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>34</x:v>
@@ -2307,16 +2283,16 @@
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
         <x:v>34</x:v>
@@ -2324,121 +2300,121 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
@@ -2446,33 +2422,33 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
@@ -2489,24 +2465,24 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
@@ -2514,33 +2490,33 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
@@ -2548,38 +2524,38 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>82</x:v>
@@ -2588,78 +2564,78 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
@@ -2667,38 +2643,38 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>82</x:v>
@@ -2707,265 +2683,265 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="E87" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="E88" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E98" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D99" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E99" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D100" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E100" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
@@ -2973,33 +2949,33 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
@@ -3007,10 +2983,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>64</x:v>
@@ -3021,13 +2997,13 @@
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>64</x:v>
@@ -3041,10 +3017,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>64</x:v>
@@ -3055,7 +3031,7 @@
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>82</x:v>
@@ -3075,21 +3051,21 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>82</x:v>
@@ -3098,44 +3074,44 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C109" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E109" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D110" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E110" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
@@ -3143,33 +3119,33 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
@@ -3177,10 +3153,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>73</x:v>
@@ -3191,7 +3167,7 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>82</x:v>
@@ -3200,10 +3176,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
@@ -3211,67 +3187,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:11">
-      <x:c r="A116" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E116" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:11">
-      <x:c r="A117" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E117" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:11">
-      <x:c r="A118" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E118" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,202 +49,196 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.08.2026</x:t>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
   </x:si>
   <x:si>
     <x:t>25.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKSLN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
     <x:t>23.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
@@ -640,7 +634,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K115"/>
+  <x:dimension ref="A1:K109"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -698,19 +692,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -730,22 +724,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -765,22 +759,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -803,19 +797,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -832,30 +826,30 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -867,30 +861,30 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -899,19 +893,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>14</x:v>
@@ -925,37 +919,37 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -969,28 +963,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -1004,19 +998,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>15</x:v>
@@ -1030,7 +1024,7 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -1039,68 +1033,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>273.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-9.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1109,33 +1103,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="0">
         <x:v>0</x:v>
@@ -1144,33 +1138,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1179,33 +1173,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1217,65 +1211,65 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>9.34</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>-9.93</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1284,33 +1278,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1319,33 +1313,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1357,25 +1351,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1389,19 +1383,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
         <x:v>14</x:v>
@@ -1415,7 +1409,7 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="0">
         <x:v>0</x:v>
@@ -1424,33 +1418,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B24" s="0">
         <x:v>0</x:v>
@@ -1459,33 +1453,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1494,19 +1488,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
         <x:v>15</x:v>
@@ -1520,147 +1514,147 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>2.48</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>-2.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
+      <x:c r="E29" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1669,68 +1663,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B32" s="0">
         <x:v>0</x:v>
@@ -1739,33 +1733,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B33" s="0">
         <x:v>0</x:v>
@@ -1774,120 +1768,84 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:11">
-      <x:c r="A34" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G34" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H34" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I34" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J34" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
+    </x:row>
+    <x:row r="36" spans="1:11">
+      <x:c r="A36" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H35" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I35" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J35" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K35" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C36" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
@@ -1895,13 +1853,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
         <x:v>13</x:v>
@@ -1909,16 +1867,16 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
         <x:v>13</x:v>
@@ -1943,13 +1901,13 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>17</x:v>
@@ -1963,10 +1921,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>17</x:v>
@@ -1977,7 +1935,7 @@
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>80</x:v>
@@ -1986,10 +1944,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -1997,10 +1955,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>20</x:v>
@@ -2011,41 +1969,41 @@
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>80</x:v>
@@ -2057,29 +2015,29 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>80</x:v>
@@ -2088,117 +2046,117 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E54" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>80</x:v>
@@ -2207,15 +2165,15 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>80</x:v>
@@ -2224,27 +2182,27 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
@@ -2252,16 +2210,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -2269,50 +2227,50 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
@@ -2320,16 +2278,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -2337,21 +2295,21 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>80</x:v>
@@ -2360,49 +2318,49 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>80</x:v>
@@ -2411,66 +2369,66 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>80</x:v>
@@ -2482,7 +2440,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
@@ -2490,16 +2448,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
@@ -2507,72 +2465,72 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>80</x:v>
@@ -2581,15 +2539,15 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>80</x:v>
@@ -2598,7 +2556,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>47</x:v>
@@ -2606,16 +2564,16 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>47</x:v>
@@ -2623,36 +2581,36 @@
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
@@ -2660,16 +2618,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -2680,149 +2638,149 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E91" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E92" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="E93" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -2830,16 +2788,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
@@ -2847,84 +2805,84 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E98" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D99" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E99" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -2932,16 +2890,16 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
@@ -2955,44 +2913,44 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
+      <x:c r="E102" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D103" s="0" t="s">
+      <x:c r="E103" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="E103" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -3000,16 +2958,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
@@ -3017,38 +2975,38 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>80</x:v>
@@ -3057,32 +3015,32 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>80</x:v>
@@ -3091,112 +3049,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:11">
-      <x:c r="A110" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D110" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E110" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:11">
-      <x:c r="A111" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C111" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D111" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E111" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:11">
-      <x:c r="A112" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C112" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D112" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E112" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:11">
-      <x:c r="A113" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D113" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E113" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:11">
-      <x:c r="A114" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C114" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D114" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E114" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:11">
-      <x:c r="A115" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E115" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -1870,10 +1870,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>17</x:v>
@@ -1887,10 +1887,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>17</x:v>
@@ -1904,10 +1904,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>17</x:v>
@@ -1921,10 +1921,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>17</x:v>
@@ -1938,10 +1938,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>20</x:v>
@@ -1955,10 +1955,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>20</x:v>
@@ -1972,10 +1972,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>23</x:v>
@@ -1989,10 +1989,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>23</x:v>
@@ -2006,10 +2006,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>23</x:v>
@@ -2023,10 +2023,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>23</x:v>
@@ -2040,10 +2040,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>27</x:v>
@@ -2057,10 +2057,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>27</x:v>
@@ -2142,10 +2142,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>30</x:v>
@@ -2159,10 +2159,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>30</x:v>
@@ -2176,10 +2176,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>30</x:v>
@@ -2193,10 +2193,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>30</x:v>
@@ -2244,10 +2244,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>34</x:v>
@@ -2261,10 +2261,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>34</x:v>
@@ -2380,10 +2380,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>34</x:v>
@@ -2397,10 +2397,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>34</x:v>
@@ -2448,10 +2448,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>43</x:v>
@@ -2465,10 +2465,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>43</x:v>
@@ -2482,10 +2482,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>46</x:v>
@@ -2499,10 +2499,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>46</x:v>
@@ -2754,10 +2754,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>54</x:v>
@@ -2771,10 +2771,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>54</x:v>
@@ -2788,10 +2788,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>58</x:v>
@@ -2805,10 +2805,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>58</x:v>
@@ -2924,10 +2924,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>63</x:v>
@@ -2941,10 +2941,10 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>63</x:v>
@@ -3026,10 +3026,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>73</x:v>
@@ -3043,10 +3043,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>73</x:v>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,39 +49,21 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2026</x:t>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
   </x:si>
   <x:si>
     <x:t>Evet</x:t>
   </x:si>
   <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>DSTKF</x:t>
   </x:si>
   <x:si>
@@ -274,16 +256,16 @@
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEIAK</x:t>
   </x:si>
   <x:si>
     <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -634,7 +616,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K109"/>
+  <x:dimension ref="A1:K99"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -692,19 +674,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -721,30 +703,30 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>0</x:v>
@@ -756,30 +738,30 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -788,19 +770,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>15</x:v>
@@ -814,7 +796,7 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -823,28 +805,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -858,28 +840,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -893,19 +875,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>14</x:v>
@@ -919,7 +901,7 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -928,33 +910,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0">
         <x:v>0</x:v>
@@ -963,33 +945,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -998,68 +980,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>0</x:v>
+        <x:v>-5.1519</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1068,33 +1050,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1106,65 +1088,65 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1173,33 +1155,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1208,33 +1190,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1246,25 +1228,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1278,19 +1260,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>15</x:v>
@@ -1304,7 +1286,7 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B20" s="0">
         <x:v>0</x:v>
@@ -1313,33 +1295,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="0">
         <x:v>0</x:v>
@@ -1348,33 +1330,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B22" s="0">
         <x:v>0</x:v>
@@ -1383,19 +1365,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
         <x:v>14</x:v>
@@ -1409,77 +1391,77 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B25" s="0">
         <x:v>0</x:v>
@@ -1488,68 +1470,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
+      <x:c r="E26" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1558,68 +1540,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B29" s="0">
         <x:v>0</x:v>
@@ -1628,33 +1610,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="0">
         <x:v>0</x:v>
@@ -1663,342 +1645,288 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:11">
-      <x:c r="A31" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F31" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G31" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H31" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I31" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J31" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F32" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H32" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I32" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J32" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K32" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:11">
+      <x:c r="A34" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
+      <x:c r="C34" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F33" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G33" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H33" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I33" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J33" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K33" s="0" t="s">
-        <x:v>15</x:v>
+      <x:c r="D34" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
         <x:v>75</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -2006,16 +1934,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -2023,16 +1951,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -2040,16 +1968,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
@@ -2057,118 +1985,118 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
@@ -2176,16 +2104,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
@@ -2193,16 +2121,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
@@ -2210,16 +2138,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
@@ -2227,16 +2155,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
@@ -2244,16 +2172,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
@@ -2261,166 +2189,166 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>41</x:v>
@@ -2428,16 +2356,16 @@
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
         <x:v>41</x:v>
@@ -2445,7 +2373,7 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>80</x:v>
@@ -2457,24 +2385,24 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
@@ -2482,16 +2410,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
@@ -2499,118 +2427,118 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E82" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
@@ -2618,16 +2546,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -2635,424 +2563,254 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:11">
-      <x:c r="A100" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D100" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E100" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:11">
-      <x:c r="A101" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E101" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:11">
-      <x:c r="A102" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E102" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:11">
-      <x:c r="A103" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D103" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E103" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:11">
-      <x:c r="A104" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C104" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D104" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E104" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:11">
-      <x:c r="A105" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:11">
-      <x:c r="A106" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B106" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E106" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:11">
-      <x:c r="A107" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D107" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E107" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:11">
-      <x:c r="A108" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E108" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:11">
-      <x:c r="A109" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C109" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E109" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,13 +49,13 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2026</x:t>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
@@ -64,15 +64,6 @@
     <x:t>Evet</x:t>
   </x:si>
   <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.10.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
@@ -256,16 +247,16 @@
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PYAYN</x:t>
   </x:si>
   <x:si>
     <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -616,7 +607,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K99"/>
+  <x:dimension ref="A1:K96"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -700,10 +691,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>14</x:v>
@@ -726,22 +717,22 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>0</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0</x:v>
+        <x:v>-9.95</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>15</x:v>
@@ -750,13 +741,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -764,19 +755,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>0</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>15</x:v>
@@ -785,30 +776,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>0</x:v>
+        <x:v>179.6</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>-9.97</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
@@ -831,19 +822,19 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>0</x:v>
+        <x:v>31.12</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0</x:v>
+        <x:v>9.96</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
@@ -866,7 +857,7 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -875,10 +866,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -901,7 +892,7 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -910,10 +901,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -936,7 +927,7 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="0">
         <x:v>0</x:v>
@@ -945,10 +936,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -971,7 +962,7 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -980,10 +971,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>14</x:v>
@@ -1006,19 +997,19 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-5.1519</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
@@ -1041,19 +1032,19 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>14</x:v>
@@ -1158,7 +1149,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>14</x:v>
@@ -1181,7 +1172,7 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1190,10 +1181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>14</x:v>
@@ -1216,7 +1207,7 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1225,13 +1216,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>15</x:v>
@@ -1240,18 +1231,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B19" s="0">
         <x:v>0</x:v>
@@ -1260,13 +1251,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>15</x:v>
@@ -1275,30 +1266,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>9.8</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>14</x:v>
@@ -1330,10 +1321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>14</x:v>
@@ -1356,19 +1347,19 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>14</x:v>
@@ -1400,10 +1391,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>14</x:v>
@@ -1426,19 +1417,19 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>0</x:v>
+        <x:v>82.75</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0</x:v>
+        <x:v>-9.96</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>14</x:v>
@@ -1461,19 +1452,19 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>14</x:v>
@@ -1505,10 +1496,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>14</x:v>
@@ -1531,19 +1522,19 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="B27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>14</x:v>
@@ -1569,10 +1560,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>-9.26</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>61</x:v>
@@ -1634,61 +1625,43 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:11">
-      <x:c r="A30" s="0" t="s">
+    <x:row r="31" spans="1:11">
+      <x:c r="A31" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G30" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H30" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I30" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K30" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -1696,10 +1669,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>12</x:v>
@@ -1710,13 +1683,13 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
         <x:v>12</x:v>
@@ -1730,118 +1703,118 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
@@ -1849,16 +1822,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -1866,50 +1839,50 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
@@ -1917,67 +1890,67 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
@@ -1985,33 +1958,33 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
@@ -2019,152 +1992,152 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
@@ -2172,10 +2145,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>34</x:v>
@@ -2186,19 +2159,19 @@
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
@@ -2206,10 +2179,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>37</x:v>
@@ -2220,16 +2193,16 @@
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>38</x:v>
@@ -2240,50 +2213,50 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -2291,186 +2264,186 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D77" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E78" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
@@ -2478,67 +2451,67 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E82" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
@@ -2546,101 +2519,101 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D87" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E88" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
@@ -2648,67 +2621,67 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D92" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E92" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -2716,10 +2689,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>61</x:v>
@@ -2730,19 +2703,19 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
@@ -2750,67 +2723,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:11">
-      <x:c r="A97" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E97" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:11">
-      <x:c r="A98" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E98" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:11">
-      <x:c r="A99" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D99" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E99" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,39 +49,27 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.10.2026</x:t>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.09.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
   </x:si>
   <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.09.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
@@ -223,40 +211,40 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
     <x:t>Açığa Satış Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PBRUT</x:t>
   </x:si>
   <x:si>
     <x:t>03.08.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PPEGK</x:t>
   </x:si>
   <x:si>
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -607,7 +595,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K96"/>
+  <x:dimension ref="A1:K90"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -665,10 +653,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>14</x:v>
@@ -682,182 +670,182 @@
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1412</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>-9.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>60.3</x:v>
+        <x:v>34.22</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>1.77</x:v>
+        <x:v>9.96</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>179.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-9.97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>31.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>9.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>0</x:v>
@@ -866,33 +854,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -901,98 +889,98 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>0</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0</x:v>
+        <x:v>9.35</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -1006,33 +994,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="0">
         <x:v>0</x:v>
@@ -1041,33 +1029,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1076,68 +1064,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1146,19 +1134,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>14</x:v>
@@ -1172,7 +1160,7 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1181,63 +1169,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1245,34 +1233,34 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>0</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -1280,10 +1268,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>9.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>45</x:v>
@@ -1292,22 +1280,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1327,22 +1315,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1356,63 +1344,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1420,34 +1408,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>82.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-9.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1467,22 +1455,22 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1490,39 +1478,39 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>0</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0</x:v>
+        <x:v>-8.16</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B27" s="0">
         <x:v>0</x:v>
@@ -1531,108 +1519,72 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:11">
-      <x:c r="A28" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B28" s="0">
-        <x:v>0.49</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>-9.26</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G28" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H28" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I28" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J28" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:11">
+      <x:c r="A30" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
+      <x:c r="C30" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H29" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I29" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J29" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K29" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="D30" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
         <x:v>66</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>67</x:v>
@@ -1641,10 +1593,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
@@ -1655,10 +1607,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
         <x:v>13</x:v>
@@ -1675,7 +1627,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
         <x:v>13</x:v>
@@ -1683,16 +1635,16 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
         <x:v>13</x:v>
@@ -1700,16 +1652,16 @@
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
         <x:v>13</x:v>
@@ -1717,104 +1669,104 @@
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
@@ -1822,16 +1774,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -1839,16 +1791,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -1856,16 +1808,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -1873,16 +1825,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
@@ -1890,16 +1842,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
@@ -1907,16 +1859,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -1924,16 +1876,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -1941,242 +1893,242 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>71</x:v>
@@ -2185,225 +2137,225 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E71" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E72" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>45</x:v>
@@ -2414,13 +2366,13 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>45</x:v>
@@ -2431,13 +2383,13 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>45</x:v>
@@ -2448,13 +2400,13 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>45</x:v>
@@ -2465,274 +2417,172 @@
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E84" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:11">
-      <x:c r="A91" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E91" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:11">
-      <x:c r="A92" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D92" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E92" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:11">
-      <x:c r="A93" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C93" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D93" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="E93" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:11">
-      <x:c r="A94" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D94" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E94" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:11">
-      <x:c r="A95" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D95" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E95" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:11">
-      <x:c r="A96" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E96" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,60 +49,21 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.10.2026</x:t>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hayır</x:t>
   </x:si>
   <x:si>
     <x:t>Evet</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIGEN</x:t>
   </x:si>
   <x:si>
@@ -211,34 +172,31 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKISY</x:t>
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
   </x:si>
   <x:si>
     <x:t>PPEGK</x:t>
@@ -595,7 +553,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K90"/>
+  <x:dimension ref="A1:K59"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -653,10 +611,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>14</x:v>
@@ -670,7 +628,7 @@
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0">
         <x:v>0</x:v>
@@ -679,33 +637,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>0</x:v>
@@ -714,68 +672,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>34.22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>9.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -784,33 +742,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -819,68 +777,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -889,68 +847,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>9.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -959,33 +917,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -994,68 +952,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
+      <x:c r="E13" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="0">
         <x:v>0</x:v>
@@ -1064,68 +1022,68 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="0">
         <x:v>0</x:v>
@@ -1134,19 +1092,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>14</x:v>
@@ -1160,7 +1118,7 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="0">
         <x:v>0</x:v>
@@ -1169,33 +1127,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B18" s="0">
         <x:v>0</x:v>
@@ -1204,1385 +1162,696 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B19" s="0">
-        <x:v>2.08</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H19" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J20" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B21" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>0</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H21" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H22" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K23" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0</x:v>
+      <x:c r="C24" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G24" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K25" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B26" s="0">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>-8.16</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K26" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B27" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K27" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:11">
+      <x:c r="A28" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:11">
-      <x:c r="A60" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:11">
-      <x:c r="A61" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:11">
-      <x:c r="A62" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D62" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:11">
-      <x:c r="A63" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E63" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:11">
-      <x:c r="A64" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E64" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:11">
-      <x:c r="A65" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E65" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:11">
-      <x:c r="A66" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E66" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:11">
-      <x:c r="A67" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E67" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:11">
-      <x:c r="A68" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E68" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:11">
-      <x:c r="A69" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:11">
-      <x:c r="A70" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E70" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:11">
-      <x:c r="A71" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E71" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:11">
-      <x:c r="A72" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E72" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:11">
-      <x:c r="A73" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:11">
-      <x:c r="A74" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:11">
-      <x:c r="A75" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E75" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:11">
-      <x:c r="A76" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C76" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D76" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E76" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:11">
-      <x:c r="A77" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D77" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E77" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:11">
-      <x:c r="A78" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E78" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:11">
-      <x:c r="A79" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:11">
-      <x:c r="A80" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:11">
-      <x:c r="A81" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:11">
-      <x:c r="A82" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E82" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:11">
-      <x:c r="A83" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:11">
-      <x:c r="A84" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E84" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:11">
-      <x:c r="A85" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E85" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:11">
-      <x:c r="A86" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E86" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:11">
-      <x:c r="A87" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D87" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E87" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:11">
-      <x:c r="A88" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E88" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:11">
-      <x:c r="A89" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:11">
-      <x:c r="A90" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,13 +49,13 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2026</x:t>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
@@ -64,15 +64,6 @@
     <x:t>Evet</x:t>
   </x:si>
   <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.10.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
@@ -184,25 +175,25 @@
     <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
   <x:si>
+    <x:t>PPEGK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBRUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEIAK</x:t>
   </x:si>
   <x:si>
     <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -553,7 +544,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K59"/>
+  <x:dimension ref="A1:K56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -675,7 +666,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
@@ -698,7 +689,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -707,10 +698,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>14</x:v>
@@ -733,7 +724,7 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -742,13 +733,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>15</x:v>
@@ -757,18 +748,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -777,13 +768,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>15</x:v>
@@ -792,30 +783,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -847,10 +838,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -873,19 +864,19 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -917,10 +908,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>14</x:v>
@@ -943,7 +934,7 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B12" s="0">
         <x:v>0</x:v>
@@ -952,10 +943,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
@@ -978,19 +969,19 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="B13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>14</x:v>
@@ -1022,10 +1013,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>14</x:v>
@@ -1048,19 +1039,19 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>14</x:v>
@@ -1151,61 +1142,43 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="0" t="s">
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H18" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K18" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1213,10 +1186,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>12</x:v>
@@ -1227,19 +1200,19 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1247,10 +1220,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>17</x:v>
@@ -1261,16 +1234,16 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
         <x:v>18</x:v>
@@ -1281,50 +1254,50 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1332,186 +1305,186 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -1519,67 +1492,67 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
@@ -1587,101 +1560,101 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
@@ -1689,67 +1662,67 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
@@ -1757,10 +1730,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>41</x:v>
@@ -1771,19 +1744,19 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -1791,67 +1764,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:11">
-      <x:c r="A57" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:11">
-      <x:c r="A58" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E58" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:11">
-      <x:c r="A59" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E59" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,28 +49,19 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.10.2026</x:t>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
   </x:si>
   <x:si>
     <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>ARMGD</x:t>
@@ -544,7 +535,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K56"/>
+  <x:dimension ref="A1:K53"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -631,7 +622,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>14</x:v>
@@ -654,7 +645,7 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>0</x:v>
@@ -663,10 +654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
@@ -689,7 +680,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -698,13 +689,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>15</x:v>
@@ -713,18 +704,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -733,13 +724,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>15</x:v>
@@ -748,30 +739,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
@@ -803,10 +794,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -829,19 +820,19 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -873,10 +864,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -899,7 +890,7 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -908,10 +899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>14</x:v>
@@ -934,19 +925,19 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>14</x:v>
@@ -978,10 +969,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>14</x:v>
@@ -1004,19 +995,19 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="B14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>14</x:v>
@@ -1107,61 +1098,43 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="0" t="s">
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="0" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="B17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1169,10 +1142,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>12</x:v>
@@ -1183,16 +1156,16 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
         <x:v>13</x:v>
@@ -1203,50 +1176,50 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1254,186 +1227,186 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
@@ -1441,67 +1414,67 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
@@ -1509,101 +1482,101 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
@@ -1611,67 +1584,67 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
@@ -1679,10 +1652,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>38</x:v>
@@ -1693,19 +1666,19 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
@@ -1713,67 +1686,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:11">
-      <x:c r="A54" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E54" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:11">
-      <x:c r="A55" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:11">
-      <x:c r="A56" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D56" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E56" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -154,37 +154,37 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
     <x:t>Açığa Satış Yasağı</x:t>
   </x:si>
   <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
     <x:t>PPEGK</x:t>
   </x:si>
   <x:si>
     <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
   </x:si>
   <x:si>
+    <x:t>PEIAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PYAYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
+  </x:si>
+  <x:si>
     <x:t>PBRUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1159,10 +1159,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>17</x:v>
@@ -1176,10 +1176,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>17</x:v>
@@ -1193,10 +1193,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>17</x:v>
@@ -1210,10 +1210,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>17</x:v>
@@ -1227,10 +1227,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>17</x:v>
@@ -1244,10 +1244,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>17</x:v>
@@ -1261,10 +1261,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>17</x:v>
@@ -1281,7 +1281,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>17</x:v>
@@ -1295,10 +1295,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>17</x:v>
@@ -1312,10 +1312,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>17</x:v>
@@ -1329,10 +1329,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>17</x:v>
@@ -1346,10 +1346,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>17</x:v>
@@ -1465,10 +1465,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>26</x:v>
@@ -1482,10 +1482,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>26</x:v>
@@ -1499,10 +1499,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>26</x:v>
@@ -1516,10 +1516,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>26</x:v>
@@ -1533,10 +1533,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>31</x:v>
@@ -1550,10 +1550,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>31</x:v>
@@ -1601,10 +1601,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>35</x:v>
@@ -1618,10 +1618,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>35</x:v>
@@ -1635,10 +1635,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>38</x:v>
@@ -1652,10 +1652,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>38</x:v>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,13 +49,13 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.10.2026</x:t>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
@@ -64,30 +64,6 @@
     <x:t>Evet</x:t>
   </x:si>
   <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.10.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>YKSLN</x:t>
   </x:si>
   <x:si>
@@ -154,37 +130,16 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PASKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açığa Satış Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKISY</x:t>
   </x:si>
   <x:si>
     <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPEGK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Piyasa Emri ile Piyasadan Limite Emir Girişinin Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEIAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emir İptali - Miktar Azaltımı - Fiyatı Kötüleştirme Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PYAYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veri Yayınının Emir Toplama Seansında Kısıtlanması</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PBRUT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -535,7 +490,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K53"/>
+  <x:dimension ref="A1:K34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -619,7 +574,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
@@ -645,19 +600,19 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
@@ -680,22 +635,22 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>15</x:v>
@@ -704,18 +659,18 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -724,10 +679,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
@@ -750,7 +705,7 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="0">
         <x:v>0</x:v>
@@ -759,10 +714,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>14</x:v>
@@ -785,19 +740,19 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -820,7 +775,7 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -829,10 +784,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -855,7 +810,7 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0">
         <x:v>0</x:v>
@@ -864,10 +819,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>14</x:v>
@@ -890,7 +845,7 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0">
         <x:v>0</x:v>
@@ -899,10 +854,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>14</x:v>
@@ -920,782 +875,369 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>0</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I14" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B15" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>0</x:v>
+      <x:c r="C16" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I16" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:11">
-      <x:c r="A35" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:11">
-      <x:c r="A36" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:11">
-      <x:c r="A37" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:11">
-      <x:c r="A38" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:11">
-      <x:c r="A39" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:11">
-      <x:c r="A40" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:11">
-      <x:c r="A41" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:11">
-      <x:c r="A42" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:11">
-      <x:c r="A43" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:11">
-      <x:c r="A44" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:11">
-      <x:c r="A45" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:11">
-      <x:c r="A46" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:11">
-      <x:c r="A47" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:11">
-      <x:c r="A48" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:11">
-      <x:c r="A49" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:11">
-      <x:c r="A50" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:11">
-      <x:c r="A51" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E51" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:11">
-      <x:c r="A52" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:11">
-      <x:c r="A53" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>42</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,31 +49,19 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.10.2026</x:t>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
   </x:si>
   <x:si>
     <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKSLN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>CITAS</x:t>
@@ -490,7 +478,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K34"/>
+  <x:dimension ref="A1:K28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -609,10 +597,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
@@ -635,19 +623,19 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>14</x:v>
@@ -679,10 +667,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
@@ -749,10 +737,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>14</x:v>
@@ -775,7 +763,7 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0">
         <x:v>0</x:v>
@@ -784,10 +772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>14</x:v>
@@ -805,87 +793,51 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:11">
-      <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
+      <x:c r="C12" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="D12" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
         <x:v>35</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>36</x:v>
@@ -894,21 +846,21 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>12</x:v>
@@ -919,13 +871,13 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>12</x:v>
@@ -936,13 +888,13 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>12</x:v>
@@ -953,13 +905,13 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>12</x:v>
@@ -970,274 +922,172 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:11">
-      <x:c r="A29" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:11">
-      <x:c r="A30" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:11">
-      <x:c r="A31" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C31" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:11">
-      <x:c r="A32" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:11">
-      <x:c r="A33" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:11">
-      <x:c r="A34" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,34 +49,19 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.10.2026</x:t>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
   </x:si>
   <x:si>
     <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>KZGYO</x:t>
@@ -478,7 +463,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K28"/>
+  <x:dimension ref="A1:K19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -597,10 +582,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
@@ -623,7 +608,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>0</x:v>
@@ -632,10 +617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>14</x:v>
@@ -658,7 +643,7 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>0</x:v>
@@ -667,10 +652,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>14</x:v>
@@ -688,145 +673,91 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:11">
-      <x:c r="A7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D9" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:11">
+      <x:c r="A10" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="s">
+      <x:c r="C10" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="D10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>12</x:v>
@@ -837,257 +768,104 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:11">
-      <x:c r="A21" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:11">
-      <x:c r="A22" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:11">
-      <x:c r="A23" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:11">
-      <x:c r="A24" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:11">
-      <x:c r="A26" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:11">
-      <x:c r="A27" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:11">
-      <x:c r="A28" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,31 +49,19 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.10.2026</x:t>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
   </x:si>
   <x:si>
     <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>USAK</x:t>
@@ -463,7 +451,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K19"/>
+  <x:dimension ref="A1:K13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -547,10 +535,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>14</x:v>
@@ -573,7 +561,7 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>0</x:v>
@@ -582,10 +570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
@@ -606,84 +594,48 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:11">
-      <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="C7" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="D7" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
         <x:v>26</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>27</x:v>
@@ -692,180 +644,78 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11">
-      <x:c r="A15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -689,10 +689,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>20</x:v>
@@ -706,10 +706,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>20</x:v>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,28 +49,19 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.10.2026</x:t>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
   </x:si>
   <x:si>
     <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>DMRGD</x:t>
@@ -451,7 +442,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K13"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -494,7 +485,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>0</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>0</x:v>
@@ -529,10 +520,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>0</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -559,61 +550,43 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:11">
-      <x:c r="A4" s="0" t="s">
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="0" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -621,10 +594,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>12</x:v>
@@ -635,19 +608,19 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -655,67 +628,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -49,13 +49,13 @@
     <x:t>Veri Yayını</x:t>
   </x:si>
   <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.10.2026</x:t>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>Hayır</x:t>
@@ -64,15 +64,6 @@
     <x:t>Evet</x:t>
   </x:si>
   <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.10.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>Detaylı Kısıtlamalar</x:t>
   </x:si>
   <x:si>
@@ -82,16 +73,16 @@
     <x:t>Açıklama</x:t>
   </x:si>
   <x:si>
+    <x:t>PKISY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kredili İşlem Yasağı</x:t>
+  </x:si>
+  <x:si>
     <x:t>PASKI</x:t>
   </x:si>
   <x:si>
     <x:t>Açığa Satış Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -442,7 +433,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -485,7 +476,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>0.37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>0</x:v>
@@ -515,61 +506,43 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:11">
-      <x:c r="A3" s="0" t="s">
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>6.3</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>1.45</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -577,67 +550,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:11">
-      <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:11">
-      <x:c r="A9" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:11">
-      <x:c r="A10" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
+++ b/app/borsa/tedbirli-hisseler/data/tedbir.xlsx
@@ -47,42 +47,6 @@
   </x:si>
   <x:si>
     <x:t>Veri Yayını</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hayır</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Detaylı Kısıtlamalar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açıklama</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKISY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kredili İşlem Yasağı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Açığa Satış Yasağı</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -433,7 +397,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K7"/>
+  <x:dimension ref="A1:K1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -469,97 +433,6 @@
       </x:c>
       <x:c r="K1" s="0" t="s">
         <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11">
-      <x:c r="A2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:11">
-      <x:c r="A4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:11">
-      <x:c r="A5" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:11">
-      <x:c r="A6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:11">
-      <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
